--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487123_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487123_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.6422</v>
+        <v>5.0657</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8812</v>
+        <v>2.6795</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7609</v>
+        <v>2.3862</v>
       </c>
       <c r="G2" t="n">
         <v>1.3961</v>
@@ -610,13 +610,13 @@
         <v>1.5441</v>
       </c>
       <c r="S2" t="n">
-        <v>2.825</v>
+        <v>1.2486</v>
       </c>
       <c r="T2" t="n">
-        <v>1.8376</v>
+        <v>0.6359</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9875</v>
+        <v>0.6127</v>
       </c>
       <c r="V2" t="n">
         <v>1.842</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. ARRIAZU ARBIZU</t>
+          <t>K. ABU SHAMS SANCHEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0489</v>
+        <v>4.6099</v>
       </c>
       <c r="E3" t="n">
-        <v>5.8587</v>
+        <v>3.8093</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8099</v>
+        <v>0.8006</v>
       </c>
       <c r="G3" t="n">
-        <v>4.6555</v>
+        <v>4.2433</v>
       </c>
       <c r="H3" t="n">
-        <v>4.1978</v>
+        <v>2.4054</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4577</v>
+        <v>1.8379</v>
       </c>
       <c r="J3" t="n">
-        <v>5.5693</v>
+        <v>5.584</v>
       </c>
       <c r="K3" t="n">
-        <v>4.8124</v>
+        <v>2.4994</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7569</v>
+        <v>3.0846</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9137999999999999</v>
+        <v>-1.3406</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6146</v>
+        <v>-0.094</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2992</v>
+        <v>-1.2467</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.579</v>
+        <v>1.158</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3511</v>
+        <v>2.1231</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5864</v>
+        <v>-0.7492</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9915</v>
+        <v>-0.7674</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5948</v>
+        <v>0.0181</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.614</v>
+        <v>-0.0422</v>
       </c>
       <c r="W3" t="n">
-        <v>1.228</v>
+        <v>-0.0422</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.842</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. ABU SHAMS SANCHEZ</t>
+          <t>J. ARRIAZU ARBIZU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.554</v>
+        <v>3.6192</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2085</v>
+        <v>4.8573</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3455</v>
+        <v>-1.2382</v>
       </c>
       <c r="G4" t="n">
-        <v>4.2433</v>
+        <v>4.6555</v>
       </c>
       <c r="H4" t="n">
-        <v>2.4054</v>
+        <v>4.1978</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8379</v>
+        <v>0.4577</v>
       </c>
       <c r="J4" t="n">
-        <v>5.584</v>
+        <v>5.5693</v>
       </c>
       <c r="K4" t="n">
-        <v>2.4994</v>
+        <v>4.8124</v>
       </c>
       <c r="L4" t="n">
-        <v>3.0846</v>
+        <v>0.7569</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.3406</v>
+        <v>-0.9137999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.094</v>
+        <v>-0.6146</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.2467</v>
+        <v>-0.2992</v>
       </c>
       <c r="P4" t="n">
-        <v>1.158</v>
+        <v>-0.579</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1231</v>
+        <v>1.3511</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.8052</v>
+        <v>0.1566</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.3682</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4369</v>
+        <v>0.1665</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.0422</v>
+        <v>-0.614</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.0422</v>
+        <v>1.228</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.842</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.039</v>
+        <v>2.3172</v>
       </c>
       <c r="E5" t="n">
-        <v>2.481</v>
+        <v>2.0804</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.2368</v>
       </c>
       <c r="G5" t="n">
         <v>2.2461</v>
@@ -844,13 +844,13 @@
         <v>0.772</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2717</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7403</v>
+        <v>0.3398</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5314</v>
+        <v>0.2102</v>
       </c>
       <c r="V5" t="n">
         <v>-0.2859</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0478</v>
+        <v>1.4752</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7873</v>
+        <v>2.1879</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7395</v>
+        <v>-0.7128</v>
       </c>
       <c r="G6" t="n">
         <v>1.3668</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6048</v>
+        <v>-0.1775</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1785</v>
+        <v>0.2221</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4264</v>
+        <v>-0.3996</v>
       </c>
       <c r="V6" t="n">
         <v>0.2859</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0041</v>
+        <v>0.9971</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3175</v>
+        <v>-0.2174</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3216</v>
+        <v>1.2145</v>
       </c>
       <c r="G7" t="n">
         <v>-0.2006</v>
@@ -1000,13 +1000,13 @@
         <v>2.3161</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1005</v>
+        <v>-0.1074</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2842</v>
+        <v>-0.1841</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1837</v>
+        <v>0.0766</v>
       </c>
       <c r="V7" t="n">
         <v>1.8842</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.024</v>
+        <v>0.4384</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6324</v>
+        <v>-0.4321</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6564</v>
+        <v>0.8706</v>
       </c>
       <c r="G8" t="n">
         <v>0.4603</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4363</v>
+        <v>-0.0218</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.238</v>
+        <v>-0.0377</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1983</v>
+        <v>0.0159</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3457</v>
+        <v>-1.6194</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5589</v>
+        <v>0.2584</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.9046</v>
+        <v>-1.8778</v>
       </c>
       <c r="G9" t="n">
         <v>-1.5116</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1659</v>
+        <v>-0.1077</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5486</v>
+        <v>0.2482</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3827</v>
+        <v>-0.3559</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9897</v>
+        <v>-2.1503</v>
       </c>
       <c r="E10" t="n">
         <v>-1.1697</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.82</v>
+        <v>-0.9806</v>
       </c>
       <c r="G10" t="n">
         <v>-1.5572</v>
@@ -1234,13 +1234,13 @@
         <v>1.158</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2551</v>
+        <v>-0.4158</v>
       </c>
       <c r="T10" t="n">
         <v>-0.1057</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1494</v>
+        <v>-0.31</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3704</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0107</v>
+        <v>-2.2621</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1319</v>
+        <v>-2.7313</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1212</v>
+        <v>0.4692</v>
       </c>
       <c r="G11" t="n">
         <v>-2.2488</v>
@@ -1312,13 +1312,13 @@
         <v>2.3161</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.476</v>
+        <v>-0.7274</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7006</v>
+        <v>-0.3001</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7754</v>
+        <v>-0.4274</v>
       </c>
       <c r="V11" t="n">
         <v>0.3281</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.8362</v>
+        <v>-2.9339</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.0893</v>
+        <v>-2.5886</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7469</v>
+        <v>-0.3454</v>
       </c>
       <c r="G12" t="n">
         <v>-0.0507</v>
@@ -1390,13 +1390,13 @@
         <v>0.193</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0834</v>
+        <v>-0.1811</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4759</v>
+        <v>0.0248</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6075</v>
+        <v>-0.2059</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.9645</v>
+        <v>-5.3438</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.8463</v>
+        <v>-1.1453</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.1182</v>
+        <v>-4.1985</v>
       </c>
       <c r="G13" t="n">
         <v>-3.3185</v>
@@ -1468,13 +1468,13 @@
         <v>0.772</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6762</v>
+        <v>-0.0555</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4164</v>
+        <v>0.2846</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2598</v>
+        <v>-0.3401</v>
       </c>
       <c r="V13" t="n">
         <v>-2.7418</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.2132</v>
+        <v>4.213200000000002</v>
       </c>
       <c r="E14" t="n">
-        <v>7.588500000000001</v>
+        <v>7.588399999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.3755</v>
+        <v>-3.3754</v>
       </c>
       <c r="G14" t="n">
         <v>5.480700000000001</v>
@@ -1546,13 +1546,13 @@
         <v>12.5455</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5884999999999995</v>
+        <v>-0.5883</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3505000000000004</v>
+        <v>0.3505</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9389999999999998</v>
+        <v>-0.9389000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>0.2859000000000003</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.0859</v>
+        <v>5.5247</v>
       </c>
       <c r="E15" t="n">
-        <v>8.811999999999999</v>
+        <v>8.4114</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.7261</v>
+        <v>-2.8867</v>
       </c>
       <c r="G15" t="n">
         <v>4.7361</v>
@@ -1624,13 +1624,13 @@
         <v>1.9301</v>
       </c>
       <c r="S15" t="n">
-        <v>0.427</v>
+        <v>-0.1342</v>
       </c>
       <c r="T15" t="n">
-        <v>0.546</v>
+        <v>0.1455</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.119</v>
+        <v>-0.2796</v>
       </c>
       <c r="V15" t="n">
         <v>-0.0422</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.955</v>
+        <v>4.4717</v>
       </c>
       <c r="E16" t="n">
-        <v>5.3724</v>
+        <v>4.371</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5825</v>
+        <v>0.1007</v>
       </c>
       <c r="G16" t="n">
         <v>4.3884</v>
@@ -1702,13 +1702,13 @@
         <v>2.5091</v>
       </c>
       <c r="S16" t="n">
-        <v>2.1879</v>
+        <v>0.7046</v>
       </c>
       <c r="T16" t="n">
-        <v>1.3313</v>
+        <v>0.3299</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8566</v>
+        <v>0.3747</v>
       </c>
       <c r="V16" t="n">
         <v>-0.0422</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.5233</v>
+        <v>2.8971</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8716</v>
+        <v>1.2722</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6517</v>
+        <v>1.6249</v>
       </c>
       <c r="G17" t="n">
         <v>1.0795</v>
@@ -1780,13 +1780,13 @@
         <v>1.9301</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2703</v>
+        <v>0.1035</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6715</v>
+        <v>-0.271</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4012</v>
+        <v>0.3744</v>
       </c>
       <c r="V17" t="n">
         <v>0.9421</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. DEL VAL IBAÑEZ</t>
+          <t>R. SANCHEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1261</v>
+        <v>-0.5526</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1623</v>
+        <v>0.8882</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.2884</v>
+        <v>-1.4408</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6301</v>
+        <v>-1.4053</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2866</v>
+        <v>-2.2728</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3434</v>
+        <v>0.8675</v>
       </c>
       <c r="J18" t="n">
-        <v>1.4452</v>
+        <v>0.6572</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0207</v>
+        <v>-0.6367</v>
       </c>
       <c r="L18" t="n">
-        <v>1.4245</v>
+        <v>1.2938</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.0752</v>
+        <v>-2.0624</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3073</v>
+        <v>-1.6361</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.7679</v>
+        <v>-0.4263</v>
       </c>
       <c r="P18" t="n">
-        <v>0.386</v>
+        <v>0.772</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.193</v>
       </c>
       <c r="R18" t="n">
-        <v>0.386</v>
+        <v>0.965</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5962</v>
+        <v>0.3665</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2829</v>
+        <v>0.4241</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3133</v>
+        <v>-0.0575</v>
       </c>
       <c r="V18" t="n">
         <v>-0.2859</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. SANCHEZ SANCHEZ</t>
+          <t>A. DEL VAL IBAÑEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.321</v>
+        <v>-1.0865</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3875</v>
+        <v>1.3626</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.7085</v>
+        <v>-2.449</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.4053</v>
+        <v>-0.6301</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.2728</v>
+        <v>-0.2866</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8675</v>
+        <v>-0.3434</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6572</v>
+        <v>1.4452</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6367</v>
+        <v>0.0207</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2938</v>
+        <v>1.4245</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.0624</v>
+        <v>-2.0752</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.6361</v>
+        <v>-0.3073</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4263</v>
+        <v>-1.7679</v>
       </c>
       <c r="P19" t="n">
-        <v>0.772</v>
+        <v>0.386</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.193</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.965</v>
+        <v>0.386</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4019</v>
+        <v>-0.5566</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0766</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3252</v>
+        <v>-0.4739</v>
       </c>
       <c r="V19" t="n">
         <v>-0.2859</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.8905</v>
+        <v>-1.9149</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.907</v>
+        <v>-0.3062</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9835</v>
+        <v>-1.6087</v>
       </c>
       <c r="G20" t="n">
         <v>-1.7937</v>
@@ -2014,13 +2014,13 @@
         <v>1.7371</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.934</v>
+        <v>-0.9584</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.2492</v>
+        <v>-0.6484</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6848</v>
+        <v>-0.31</v>
       </c>
       <c r="V20" t="n">
         <v>-0.8999</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. GUTIERREZ O´CALLAGHAN</t>
+          <t>I. HANSEN GUTIERREZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.7266</v>
+        <v>-3.5141</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.5917</v>
+        <v>-3.2431</v>
       </c>
       <c r="F21" t="n">
-        <v>1.8651</v>
+        <v>-0.271</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.126</v>
+        <v>-3.2652</v>
       </c>
       <c r="H21" t="n">
-        <v>-4.9371</v>
+        <v>-1.453</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8111</v>
+        <v>-1.8122</v>
       </c>
       <c r="J21" t="n">
-        <v>-4.0862</v>
+        <v>-2.3841</v>
       </c>
       <c r="K21" t="n">
-        <v>-4.249</v>
+        <v>-0.5848</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1628</v>
+        <v>-1.7993</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0398</v>
+        <v>-0.8811</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6881</v>
+        <v>-0.8682</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6483</v>
+        <v>-0.0129</v>
       </c>
       <c r="P21" t="n">
-        <v>-5.0182</v>
+        <v>-0.193</v>
       </c>
       <c r="Q21" t="n">
-        <v>-5.9833</v>
+        <v>-1.158</v>
       </c>
       <c r="R21" t="n">
         <v>0.965</v>
       </c>
       <c r="S21" t="n">
-        <v>3.8615</v>
+        <v>-0.0559</v>
       </c>
       <c r="T21" t="n">
-        <v>2.9639</v>
+        <v>0.2991</v>
       </c>
       <c r="U21" t="n">
-        <v>0.8976</v>
+        <v>-0.355</v>
       </c>
       <c r="V21" t="n">
-        <v>1.5561</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.5138</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.0422</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. HANSEN GUTIERREZ</t>
+          <t>S. HANSEN GUTIERREZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.4827</v>
+        <v>-4.1348</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.944</v>
+        <v>-1.9866</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5387</v>
+        <v>-2.1481</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.2652</v>
+        <v>-4.4644</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.453</v>
+        <v>-1.7583</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.8122</v>
+        <v>-2.7061</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.3841</v>
+        <v>-1.5676</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5848</v>
+        <v>0.3053</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.7993</v>
+        <v>-1.8728</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8811</v>
+        <v>-2.8968</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8682</v>
+        <v>-2.0636</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0129</v>
+        <v>-0.8333</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.193</v>
+        <v>2.1231</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.158</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.965</v>
+        <v>2.1231</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0245</v>
+        <v>-0.5655</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4019</v>
+        <v>-0.419</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6227</v>
+        <v>-0.1464</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. HANSEN GUTIERREZ</t>
+          <t>E. GUTIERREZ O´CALLAGHAN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.2303</v>
+        <v>-5.9039</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.7877</v>
+        <v>-7.3942</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.4426</v>
+        <v>1.4903</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.4644</v>
+        <v>-4.126</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.7583</v>
+        <v>-4.9371</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.7061</v>
+        <v>0.8111</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.5676</v>
+        <v>-4.0862</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3053</v>
+        <v>-4.249</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.8728</v>
+        <v>0.1628</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.8968</v>
+        <v>-0.0398</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.0636</v>
+        <v>-0.6881</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.8333</v>
+        <v>0.6483</v>
       </c>
       <c r="P23" t="n">
-        <v>2.1231</v>
+        <v>-5.0182</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-5.9833</v>
       </c>
       <c r="R23" t="n">
-        <v>2.1231</v>
+        <v>0.965</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.661</v>
+        <v>1.6842</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.2201</v>
+        <v>1.1614</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4409</v>
+        <v>0.5228</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.228</v>
+        <v>1.5561</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.5138</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.228</v>
+        <v>0.0422</v>
       </c>
     </row>
     <row r="24">
@@ -2281,28 +2281,28 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.212999999999999</v>
+        <v>-4.2133</v>
       </c>
       <c r="E24" t="n">
-        <v>3.375399999999998</v>
+        <v>3.375300000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-7.588500000000002</v>
+        <v>-7.5884</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.480699999999998</v>
+        <v>-5.480700000000001</v>
       </c>
       <c r="H24" t="n">
         <v>-11.6176</v>
       </c>
       <c r="I24" t="n">
-        <v>6.137000000000001</v>
+        <v>6.137</v>
       </c>
       <c r="J24" t="n">
         <v>8.968999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.06359999999999999</v>
+        <v>-0.06359999999999921</v>
       </c>
       <c r="L24" t="n">
         <v>9.0326</v>
@@ -2317,7 +2317,7 @@
         <v>-2.8956</v>
       </c>
       <c r="P24" t="n">
-        <v>0.9650000000000003</v>
+        <v>0.9649999999999999</v>
       </c>
       <c r="Q24" t="n">
         <v>-12.5454</v>
@@ -2326,16 +2326,16 @@
         <v>13.5105</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5884999999999998</v>
+        <v>0.5881999999999998</v>
       </c>
       <c r="T24" t="n">
-        <v>0.9390000000000005</v>
+        <v>0.9390000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3505000000000001</v>
+        <v>-0.3504999999999999</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.2858999999999998</v>
+        <v>-0.2859</v>
       </c>
       <c r="W24" t="n">
         <v>6.0131</v>
